--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484744_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484744_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4223</v>
+        <v>10.1211</v>
       </c>
       <c r="E2" t="n">
-        <v>8.539099999999999</v>
+        <v>9.026300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8832</v>
+        <v>1.0948</v>
       </c>
       <c r="G2" t="n">
         <v>8.4459</v>
@@ -610,13 +610,13 @@
         <v>0.9435</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9765</v>
+        <v>1.6753</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0617</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9147999999999999</v>
+        <v>1.1264</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.9558</v>
+        <v>9.647500000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5322</v>
+        <v>8.4091</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4235</v>
+        <v>1.2383</v>
       </c>
       <c r="G3" t="n">
         <v>9.4771</v>
@@ -688,13 +688,13 @@
         <v>0.7548</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9318</v>
+        <v>1.6236</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7642</v>
+        <v>0.1127</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6961</v>
+        <v>1.5109</v>
       </c>
       <c r="V3" t="n">
         <v>1.566</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.1507</v>
+        <v>6.0357</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7657</v>
+        <v>4.8888</v>
       </c>
       <c r="F4" t="n">
-        <v>1.385</v>
+        <v>1.1469</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1049</v>
@@ -766,13 +766,13 @@
         <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7277</v>
+        <v>1.6127</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1968</v>
+        <v>0.3199</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5309</v>
+        <v>1.2928</v>
       </c>
       <c r="V4" t="n">
         <v>4.3392</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CARR</t>
+          <t>E. RHAIEM SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8652</v>
+        <v>2.5302</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0153</v>
+        <v>1.3788</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8805</v>
+        <v>1.1514</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2201</v>
+        <v>1.6376</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7718</v>
+        <v>0.9274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5517</v>
+        <v>0.7103</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4847</v>
+        <v>1.498</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9939</v>
+        <v>1.4157</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5091</v>
+        <v>0.0823</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7353</v>
+        <v>0.1397</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7779</v>
+        <v>-0.4883</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0426</v>
+        <v>0.628</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.774</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.9062</v>
+        <v>-0.1887</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2685</v>
+        <v>0.5151</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2556</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>2.0129</v>
+        <v>0.4456</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1506</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1506</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. RHAIEM SANCHEZ</t>
+          <t>J. CARR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3437</v>
+        <v>1.8838</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0865</v>
+        <v>-1.5999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2572</v>
+        <v>3.4836</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6376</v>
+        <v>1.2201</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9274</v>
+        <v>1.7718</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7103</v>
+        <v>-0.5517</v>
       </c>
       <c r="J6" t="n">
-        <v>1.498</v>
+        <v>0.4847</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4157</v>
+        <v>0.9939</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0823</v>
+        <v>-0.5091</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1397</v>
+        <v>0.7353</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4883</v>
+        <v>0.7779</v>
       </c>
       <c r="O6" t="n">
-        <v>0.628</v>
+        <v>-0.0426</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>-3.774</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1887</v>
+        <v>-4.9062</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5661</v>
+        <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3286</v>
+        <v>2.2871</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2228</v>
+        <v>0.671</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5514</v>
+        <v>1.6161</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.1506</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1506</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7648</v>
+        <v>0.6577</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1331</v>
+        <v>-0.1592</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6317</v>
+        <v>0.8169</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2976</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3268</v>
+        <v>1.2197</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.4189</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6155</v>
+        <v>0.8007</v>
       </c>
       <c r="V7" t="n">
         <v>0.9244</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3023</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6442</v>
+        <v>-0.5467</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9465</v>
+        <v>1.1581</v>
       </c>
       <c r="G9" t="n">
         <v>1.3987</v>
@@ -1156,13 +1156,13 @@
         <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1528</v>
+        <v>0.1562</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.164</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0112</v>
+        <v>0.2228</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. PAREDES PEREZ</t>
+          <t>S. SUAREZ BELLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2307</v>
+        <v>0.0141</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8548</v>
+        <v>0.7792</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0855</v>
+        <v>-0.7651</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6887</v>
+        <v>-0.5605</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4289</v>
+        <v>0.695</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2598</v>
+        <v>-1.2555</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2569</v>
+        <v>0.7607</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6073</v>
+        <v>0.7607</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6496</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5682</v>
+        <v>-1.3212</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1784</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3897</v>
+        <v>-1.2555</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1081</v>
+        <v>0.1972</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5908</v>
+        <v>0.0185</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5173</v>
+        <v>0.1787</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. SUAREZ BELLO</t>
+          <t>I. PAREDES PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3659</v>
+        <v>-0.1674</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5843</v>
+        <v>-1.1471</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9503</v>
+        <v>0.9797</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5605</v>
+        <v>-0.6887</v>
       </c>
       <c r="H11" t="n">
-        <v>0.695</v>
+        <v>-0.4289</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2555</v>
+        <v>-0.2598</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7607</v>
+        <v>-1.2569</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7607</v>
+        <v>-0.6073</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.6496</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3212</v>
+        <v>0.5682</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.1784</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2555</v>
+        <v>0.3897</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3774</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1828</v>
+        <v>0.71</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1764</v>
+        <v>0.2985</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0065</v>
+        <v>0.4115</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3853</v>
+        <v>-0.1737</v>
       </c>
       <c r="E12" t="n">
         <v>-1.4436</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0583</v>
+        <v>1.2699</v>
       </c>
       <c r="G12" t="n">
         <v>0.574</v>
@@ -1390,13 +1390,13 @@
         <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8712</v>
+        <v>1.0829</v>
       </c>
       <c r="T12" t="n">
         <v>0.2504</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6208</v>
+        <v>0.8325</v>
       </c>
       <c r="V12" t="n">
         <v>0.6226</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6182</v>
+        <v>-1.4943</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5158</v>
+        <v>-0.4184</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1024</v>
+        <v>-1.0759</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5693</v>
@@ -1468,13 +1468,13 @@
         <v>0.1887</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6302</v>
+        <v>0.7541</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1205</v>
+        <v>0.2179</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5097</v>
+        <v>0.5362</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8678</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30.28309999999999</v>
+        <v>30.2831</v>
       </c>
       <c r="E14" t="n">
-        <v>19.7842</v>
+        <v>19.78430000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>10.4987</v>
+        <v>10.4986</v>
       </c>
       <c r="G14" t="n">
         <v>20.1494</v>
@@ -1528,13 +1528,13 @@
         <v>11.3635</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.9292</v>
+        <v>-2.929200000000001</v>
       </c>
       <c r="N14" t="n">
         <v>0.9627000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.8921</v>
+        <v>-3.892100000000001</v>
       </c>
       <c r="P14" t="n">
         <v>-9.434999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>6.6045</v>
       </c>
       <c r="S14" t="n">
-        <v>11.8338</v>
+        <v>11.8339</v>
       </c>
       <c r="T14" t="n">
-        <v>2.859599999999999</v>
+        <v>2.8596</v>
       </c>
       <c r="U14" t="n">
-        <v>8.974100000000002</v>
+        <v>8.9742</v>
       </c>
       <c r="V14" t="n">
         <v>7.735</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.323</v>
+        <v>2.1425</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6657</v>
+        <v>1.2759</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6573</v>
+        <v>0.8665</v>
       </c>
       <c r="G15" t="n">
         <v>1.7968</v>
@@ -1624,13 +1624,13 @@
         <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1487</v>
+        <v>-0.0318</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3556</v>
+        <v>-0.0341</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2069</v>
+        <v>0.0024</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.319</v>
+        <v>1.408</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2089</v>
+        <v>5.4038</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.89</v>
+        <v>-3.9958</v>
       </c>
       <c r="G16" t="n">
         <v>2.0592</v>
@@ -1702,13 +1702,13 @@
         <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1557</v>
+        <v>-2.0666</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.9618</v>
+        <v>-1.7669</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1939</v>
+        <v>-0.2997</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2828</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>R. AMOROS PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.133</v>
+        <v>-0.0732</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2774</v>
+        <v>-0.22</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1445</v>
+        <v>0.1467</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09</v>
+        <v>0.2022</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-1.9346</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7599</v>
+        <v>2.1368</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7152</v>
+        <v>1.5034</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1111</v>
+        <v>-1.0878</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6041</v>
+        <v>2.5912</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6252</v>
+        <v>-1.3012</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.781</v>
+        <v>-0.8467</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8442</v>
+        <v>-0.4544</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6983</v>
+        <v>1.3209</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0893</v>
+        <v>-1.5963</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7396</v>
+        <v>-0.7798</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6502</v>
+        <v>-0.8165</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.566</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. AMOROS PEREZ</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4797</v>
+        <v>-0.1219</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4148</v>
+        <v>1.4723</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0649</v>
+        <v>-1.5942</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2022</v>
+        <v>0.09</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9346</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1368</v>
+        <v>0.7599</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5034</v>
+        <v>1.7152</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0878</v>
+        <v>0.1111</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5912</v>
+        <v>1.6041</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3012</v>
+        <v>-1.6252</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8467</v>
+        <v>-0.781</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4544</v>
+        <v>-0.8442</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2644</v>
+        <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0028</v>
+        <v>-0.3442</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9747</v>
+        <v>-0.5447</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0281</v>
+        <v>0.2005</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.566</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3654</v>
+        <v>-2.0155</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5851</v>
+        <v>1.4877</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.9506</v>
+        <v>-3.5032</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5241</v>
@@ -2014,13 +2014,13 @@
         <v>2.8305</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.4832</v>
+        <v>-2.1332</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5597</v>
+        <v>-1.6571</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9235</v>
+        <v>-0.4761</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2452</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.12</v>
+        <v>-2.7604</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5673</v>
+        <v>-1.4699</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5527</v>
+        <v>-1.2905</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8431</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6543</v>
+        <v>-0.2947</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3016</v>
+        <v>-0.0394</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6226</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7423</v>
+        <v>-4.0611</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0954</v>
+        <v>-3.3877</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.647</v>
+        <v>-0.6734</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1833</v>
@@ -2170,13 +2170,13 @@
         <v>0.5661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1817</v>
+        <v>-0.5004</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0617</v>
+        <v>-0.2306</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2433</v>
+        <v>-0.2698</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.222</v>
+        <v>-7.0754</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4995</v>
+        <v>-5.6944</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7225</v>
+        <v>-1.381</v>
       </c>
       <c r="G23" t="n">
         <v>-7.6752</v>
@@ -2248,13 +2248,13 @@
         <v>3.0192</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.566</v>
+        <v>-2.4194</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6061</v>
+        <v>-1.801</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9599</v>
+        <v>-0.6183</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.4564</v>
+        <v>-8.1557</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1773</v>
+        <v>-5.9825</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.279</v>
+        <v>-2.1732</v>
       </c>
       <c r="G24" t="n">
         <v>-8.0684</v>
@@ -2326,13 +2326,13 @@
         <v>1.887</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6713</v>
+        <v>-1.3706</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3862</v>
+        <v>-1.1914</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2851</v>
+        <v>-0.1793</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6036</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.289</v>
+        <v>-9.537800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0985</v>
+        <v>-4.0011</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.1905</v>
+        <v>-5.5368</v>
       </c>
       <c r="G25" t="n">
         <v>-3.6204</v>
@@ -2404,13 +2404,13 @@
         <v>0.7548</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1781</v>
+        <v>-0.4269</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8107</v>
+        <v>-0.7133</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.2863</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4148</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-30.2828</v>
+        <v>-29.6335</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.4987</v>
+        <v>-10.4989</v>
       </c>
       <c r="F26" t="n">
-        <v>-19.7844</v>
+        <v>-19.1349</v>
       </c>
       <c r="G26" t="n">
         <v>-20.1493</v>
@@ -2482,16 +2482,16 @@
         <v>16.0395</v>
       </c>
       <c r="S26" t="n">
-        <v>-11.8337</v>
+        <v>-11.1841</v>
       </c>
       <c r="T26" t="n">
-        <v>-8.974200000000002</v>
+        <v>-8.9742</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8595</v>
+        <v>-2.2099</v>
       </c>
       <c r="V26" t="n">
-        <v>-7.734999999999999</v>
+        <v>-7.735000000000001</v>
       </c>
       <c r="W26" t="n">
         <v>2.1506</v>
